--- a/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630776273</v>
+        <v>10.84497618605175</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907185670592</v>
+        <v>37.78907143260677</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.910923000820798</v>
+        <v>6.429465715112362</v>
       </c>
       <c r="C2" t="n">
-        <v>7.324819621385452</v>
+        <v>9.02422489743668</v>
       </c>
       <c r="D2" t="n">
-        <v>34.46032616676729</v>
+        <v>23.36068662255285</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.8059991696534</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55198855616074</v>
+        <v>30.2280118137593</v>
       </c>
       <c r="D3" t="n">
-        <v>76.84139281139785</v>
+        <v>71.7608484419206</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.87823189360694</v>
+        <v>35.91429451675682</v>
       </c>
       <c r="C4" t="n">
-        <v>51.77835566968103</v>
+        <v>68.7655361962636</v>
       </c>
       <c r="D4" t="n">
-        <v>116.0003634906904</v>
+        <v>88.33078619419827</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.80544369477245</v>
+        <v>43.85957868722626</v>
       </c>
       <c r="C5" t="n">
-        <v>90.32078879070657</v>
+        <v>111.8701508989241</v>
       </c>
       <c r="D5" t="n">
-        <v>84.72482687649975</v>
+        <v>61.5801247488812</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.8466360406218</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0165701755771</v>
+        <v>151.4669810543107</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1258943569844</v>
+        <v>43.47178834404877</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="C7" t="n">
-        <v>81.74522259411066</v>
+        <v>156.663371652889</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.85660808191773</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>48.9843017033946</v>
+        <v>104.5610392408065</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>52.14062057254808</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689227601088385</v>
+        <v>7.650896095638282</v>
       </c>
       <c r="C21" t="n">
-        <v>94.19303811333272</v>
+        <v>92.76711515961416</v>
       </c>
       <c r="D21" t="n">
-        <v>8.650381051224434</v>
+        <v>7.650896095638282</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.85201813856599</v>
+        <v>6.730862260316131</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14970867713103</v>
+        <v>13.78079252451248</v>
       </c>
       <c r="D2" t="n">
-        <v>29.56827735650543</v>
+        <v>28.57671217521616</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.55841882173396</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31007771028852</v>
+        <v>32.41240045570844</v>
       </c>
       <c r="D3" t="n">
-        <v>84.65610453720245</v>
+        <v>72.81622722398593</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.64850293081319</v>
+        <v>34.31895449735575</v>
       </c>
       <c r="C4" t="n">
-        <v>63.46900733185205</v>
+        <v>71.85411447382405</v>
       </c>
       <c r="D4" t="n">
-        <v>125.0236066404228</v>
+        <v>99.88104793466199</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.38315331322608</v>
+        <v>48.47379289718628</v>
       </c>
       <c r="C5" t="n">
-        <v>92.77515805132359</v>
+        <v>117.4415691205247</v>
       </c>
       <c r="D5" t="n">
-        <v>104.7279363505285</v>
+        <v>76.33088400518952</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.27181491201868</v>
+        <v>48.7850069194325</v>
       </c>
       <c r="C6" t="n">
-        <v>122.4052855131966</v>
+        <v>162.375179796197</v>
       </c>
       <c r="D6" t="n">
-        <v>64.72466264558373</v>
+        <v>50.71708640139023</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.51949307092936</v>
+        <v>37.78845088416398</v>
       </c>
       <c r="C7" t="n">
-        <v>115.2817241711817</v>
+        <v>186.1874703627033</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="C8" t="n">
-        <v>76.43887625265664</v>
+        <v>150.290847304623</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.09218647320796</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>86.97499261463339</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.870605963492532</v>
+        <v>7.822323088722336</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3178775254029</v>
+        <v>100.7124097673001</v>
       </c>
       <c r="D21" t="n">
-        <v>9.838257454365666</v>
+        <v>8.800113474812628</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.778787971374978</v>
+        <v>7.211918635397069</v>
       </c>
       <c r="C2" t="n">
-        <v>14.7124710958427</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="D2" t="n">
-        <v>35.05330178013237</v>
+        <v>26.04282135055514</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.90693925674158</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="C3" t="n">
-        <v>35.70616400345649</v>
+        <v>41.43466185773664</v>
       </c>
       <c r="D3" t="n">
-        <v>87.18901361415924</v>
+        <v>76.56159471568751</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.09519813624549</v>
+        <v>34.40829353844221</v>
       </c>
       <c r="C4" t="n">
-        <v>67.77004402415733</v>
+        <v>74.78954010952202</v>
       </c>
       <c r="D4" t="n">
-        <v>135.8208678917292</v>
+        <v>109.7211051743278</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.37748381117885</v>
+        <v>49.23464736797755</v>
       </c>
       <c r="C5" t="n">
-        <v>102.3226544751238</v>
+        <v>122.2275891787279</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0677442293849</v>
+        <v>88.82362354173019</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.0869275484508</v>
+        <v>55.14476854754334</v>
       </c>
       <c r="C6" t="n">
-        <v>132.347444514104</v>
+        <v>172.840610323468</v>
       </c>
       <c r="D6" t="n">
-        <v>79.25551041614078</v>
+        <v>60.0554705641859</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.35896947351839</v>
+        <v>45.87314322863646</v>
       </c>
       <c r="C7" t="n">
-        <v>142.7097915324291</v>
+        <v>205.4110721595601</v>
       </c>
       <c r="D7" t="n">
-        <v>51.2030515149924</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.88011327355743</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="C8" t="n">
-        <v>108.6500184289945</v>
+        <v>189.3447709795611</v>
       </c>
       <c r="D8" t="n">
-        <v>41.64082887562846</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.63906100220244</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>66.67343183851361</v>
+        <v>126.9124892233936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>68.32964021557801</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>35.18387422479719</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036560567573169</v>
+        <v>7.977247160369577</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5027078041311</v>
+        <v>107.6928366649893</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05027078041311</v>
+        <v>9.971558950461972</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.095491569219199</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C2" t="n">
-        <v>10.004009106275</v>
+        <v>9.748754703170826</v>
       </c>
       <c r="D2" t="n">
-        <v>28.71219335840221</v>
+        <v>21.56899706230243</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.36054775383261</v>
+        <v>23.85156047467626</v>
       </c>
       <c r="C3" t="n">
-        <v>53.61324212891832</v>
+        <v>59.48409340031424</v>
       </c>
       <c r="D3" t="n">
-        <v>96.39780707999432</v>
+        <v>82.78587516061229</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.009662912789</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="C4" t="n">
-        <v>88.80300683994099</v>
+        <v>100.493658502112</v>
       </c>
       <c r="D4" t="n">
-        <v>131.8133737629938</v>
+        <v>103.5439486192068</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.66827675361837</v>
+        <v>31.04777114680538</v>
       </c>
       <c r="C5" t="n">
-        <v>79.07977757708059</v>
+        <v>103.2798584867645</v>
       </c>
       <c r="D5" t="n">
-        <v>79.61973881441634</v>
+        <v>59.73934780341843</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>28.45792070300229</v>
       </c>
       <c r="C6" t="n">
-        <v>93.98761646606842</v>
+        <v>135.2858153929147</v>
       </c>
       <c r="D6" t="n">
-        <v>33.6906359666378</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>76.35542769779568</v>
+        <v>133.1279339389802</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2845522699781</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>49.06775025825559</v>
+        <v>93.54582999915733</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>52.14062057254808</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61656292046278</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.956844158742146</v>
+        <v>4.023202092003429</v>
       </c>
       <c r="C2" t="n">
-        <v>4.034983064454391</v>
+        <v>5.237624002156734</v>
       </c>
       <c r="D2" t="n">
-        <v>20.55485168381547</v>
+        <v>15.16800203061322</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.02184479586747</v>
+        <v>24.07736244665303</v>
       </c>
       <c r="C3" t="n">
-        <v>47.05516746454962</v>
+        <v>49.75988238974958</v>
       </c>
       <c r="D3" t="n">
-        <v>97.25683632121027</v>
+        <v>82.21646149214914</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.40226418349649</v>
+        <v>32.7491399182651</v>
       </c>
       <c r="C4" t="n">
-        <v>114.1625317883403</v>
+        <v>126.6955229807551</v>
       </c>
       <c r="D4" t="n">
-        <v>148.5835880469378</v>
+        <v>118.4635684806456</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>34.53297549688156</v>
       </c>
       <c r="C5" t="n">
-        <v>119.061452832532</v>
+        <v>141.4943878745716</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4082464518426</v>
+        <v>75.103699374881</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>111.1348218684432</v>
+        <v>153.3588088803943</v>
       </c>
       <c r="D6" t="n">
-        <v>43.55229165579701</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>100.429844901336</v>
+        <v>162.1729397691221</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>65.50711556586842</v>
+        <v>120.4997132192535</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.128650006985338</v>
+        <v>4.112541133089889</v>
       </c>
       <c r="C2" t="n">
-        <v>4.707480241863456</v>
+        <v>9.032078879070655</v>
       </c>
       <c r="D2" t="n">
-        <v>27.69706623221101</v>
+        <v>16.67694825204057</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.61594102565702</v>
+        <v>18.90355204527233</v>
       </c>
       <c r="C3" t="n">
-        <v>30.52744486355457</v>
+        <v>34.83731728519807</v>
       </c>
       <c r="D3" t="n">
-        <v>91.46943360467532</v>
+        <v>75.82037519898117</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.77911643320702</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="C4" t="n">
-        <v>115.7833972480518</v>
+        <v>125.3171492039926</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0782910788869</v>
+        <v>130.4094745459208</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.70726892434777</v>
+        <v>40.88979188187966</v>
       </c>
       <c r="C5" t="n">
-        <v>163.8291481461865</v>
+        <v>184.6176557836127</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8109682992288</v>
+        <v>96.26036240139979</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.41645061971246</v>
+        <v>39.16486116551801</v>
       </c>
       <c r="C6" t="n">
-        <v>149.0921333577376</v>
+        <v>187.4117097498991</v>
       </c>
       <c r="D6" t="n">
-        <v>60.41773546705297</v>
+        <v>48.10072876957248</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.4404702285041</v>
+        <v>26.64954143177966</v>
       </c>
       <c r="C7" t="n">
-        <v>129.3550775115597</v>
+        <v>189.2416874706151</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>95.9658380901257</v>
+        <v>162.9750276434918</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>56.68905768632355</v>
+        <v>94.85155444580556</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.062071089545801</v>
+        <v>2.496584411899639</v>
       </c>
       <c r="C2" t="n">
-        <v>2.20696883914683</v>
+        <v>4.364850293081319</v>
       </c>
       <c r="D2" t="n">
-        <v>19.31981307187298</v>
+        <v>11.62978330450772</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.4539526544563</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>27.24840753137022</v>
+        <v>37.18860303686917</v>
       </c>
       <c r="D3" t="n">
-        <v>94.30668446994861</v>
+        <v>74.90734983403163</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.23330576737479</v>
+        <v>42.48709539668921</v>
       </c>
       <c r="C4" t="n">
-        <v>112.5927172092497</v>
+        <v>124.0664026287822</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1608400015017</v>
+        <v>138.9477343297553</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.42532740677969</v>
+        <v>42.26423866782519</v>
       </c>
       <c r="C5" t="n">
-        <v>201.7736969153258</v>
+        <v>224.2311756499715</v>
       </c>
       <c r="D5" t="n">
-        <v>132.4623089955009</v>
+        <v>101.8563243156066</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>31.71830482880595</v>
       </c>
       <c r="C6" t="n">
-        <v>178.3550871782223</v>
+        <v>224.8054980569559</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>47.33594730796422</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>131.4511088601267</v>
+        <v>202.5964014914845</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>70.93127163183205</v>
+        <v>117.8293594637022</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
         <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.164573761414969</v>
+        <v>3.119994204096364</v>
       </c>
       <c r="C2" t="n">
-        <v>4.787001805907448</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="D2" t="n">
-        <v>14.36689590394782</v>
+        <v>13.39202043363074</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.21003725544659</v>
+        <v>13.82300767579509</v>
       </c>
       <c r="C3" t="n">
-        <v>17.74999849278233</v>
+        <v>27.29749491658256</v>
       </c>
       <c r="D3" t="n">
-        <v>89.18196145378026</v>
+        <v>67.84367510197583</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.73632044484766</v>
+        <v>39.55166976099125</v>
       </c>
       <c r="C4" t="n">
-        <v>91.68738159501812</v>
+        <v>109.121257327033</v>
       </c>
       <c r="D4" t="n">
-        <v>177.3252338364674</v>
+        <v>143.2870591825262</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.93631923907354</v>
+        <v>51.00179323562181</v>
       </c>
       <c r="C5" t="n">
-        <v>206.0197557361932</v>
+        <v>227.9127295408971</v>
       </c>
       <c r="D5" t="n">
-        <v>156.7360209830033</v>
+        <v>122.5466571826081</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.79758971313847</v>
+        <v>40.89568236810514</v>
       </c>
       <c r="C6" t="n">
-        <v>241.4696835888413</v>
+        <v>282.6471275480652</v>
       </c>
       <c r="D6" t="n">
-        <v>79.17500710439252</v>
+        <v>63.23535137824131</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>186.4270168025396</v>
+        <v>256.8536701143888</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>111.8210635137117</v>
+        <v>176.4936935309703</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>50.03280825153018</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.020837685967436</v>
+        <v>2.175552912610932</v>
       </c>
       <c r="C2" t="n">
-        <v>2.905973204570559</v>
+        <v>4.466952054322987</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2955881744363</v>
+        <v>10.70890395792421</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09084487260522</v>
+        <v>12.59582304548658</v>
       </c>
       <c r="C3" t="n">
-        <v>18.30468594568178</v>
+        <v>25.91323065359456</v>
       </c>
       <c r="D3" t="n">
-        <v>83.10003442597127</v>
+        <v>64.16212121105029</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.47807974090174</v>
+        <v>35.18681946790993</v>
       </c>
       <c r="C4" t="n">
-        <v>74.04930234051992</v>
+        <v>94.29097650668065</v>
       </c>
       <c r="D4" t="n">
-        <v>180.4393375543383</v>
+        <v>144.435703996495</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.90043654237292</v>
+        <v>55.54237636776331</v>
       </c>
       <c r="C5" t="n">
-        <v>199.073890728647</v>
+        <v>225.6792535137356</v>
       </c>
       <c r="D5" t="n">
-        <v>172.9348581030757</v>
+        <v>137.3219601315226</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>47.33594730796422</v>
       </c>
       <c r="C6" t="n">
-        <v>280.3930348191146</v>
+        <v>320.9264522843526</v>
       </c>
       <c r="D6" t="n">
-        <v>95.91969594802613</v>
+        <v>74.3045567436241</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>239.7859862760579</v>
+        <v>311.230711957211</v>
       </c>
       <c r="D7" t="n">
-        <v>47.60985491744906</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>145.2004854581033</v>
+        <v>220.0538391684013</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>57.243745139223</v>
+        <v>79.43124325520091</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.060508504764808</v>
+        <v>3.029673415305656</v>
       </c>
       <c r="C2" t="n">
-        <v>12.08924123009522</v>
+        <v>8.829838851995813</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64338890364693</v>
+        <v>18.31057643190726</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.25850274585317</v>
+        <v>10.12672756930585</v>
       </c>
       <c r="C3" t="n">
-        <v>14.95201753567892</v>
+        <v>21.93224371287374</v>
       </c>
       <c r="D3" t="n">
-        <v>73.98450699203964</v>
+        <v>58.96867585558466</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.85422798034851</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>61.32487034577701</v>
+        <v>81.46444275069608</v>
       </c>
       <c r="D4" t="n">
-        <v>180.0819813899924</v>
+        <v>143.0445674995773</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.59962083424588</v>
+        <v>54.87969666739671</v>
       </c>
       <c r="C5" t="n">
-        <v>172.0758288618597</v>
+        <v>203.9335418646687</v>
       </c>
       <c r="D5" t="n">
-        <v>191.0481032464293</v>
+        <v>149.3483695085461</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.49323222928874</v>
+        <v>56.31206656789281</v>
       </c>
       <c r="C6" t="n">
-        <v>295.728915707154</v>
+        <v>336.3025848282662</v>
       </c>
       <c r="D6" t="n">
-        <v>118.0983583346658</v>
+        <v>92.17629195173305</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.35117224514665</v>
+        <v>28.44613973055133</v>
       </c>
       <c r="C7" t="n">
-        <v>308.0567216293812</v>
+        <v>369.7399298872082</v>
       </c>
       <c r="D7" t="n">
-        <v>58.26967149016093</v>
+        <v>48.98724694650735</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>209.8731154753619</v>
+        <v>293.2382217814798</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>101.6187413711788</v>
+        <v>144.1078002632765</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.381360077604268</v>
+        <v>6.130032665317084</v>
       </c>
       <c r="C2" t="n">
-        <v>3.39193831817273</v>
+        <v>11.48153940116645</v>
       </c>
       <c r="D2" t="n">
-        <v>14.72130682518092</v>
+        <v>6.23900666048848</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.93935262651495</v>
+        <v>2.213841073076558</v>
       </c>
       <c r="C2" t="n">
-        <v>6.962554718518379</v>
+        <v>5.226824777410018</v>
       </c>
       <c r="D2" t="n">
-        <v>13.87013156559894</v>
+        <v>13.62273114412874</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>13.53339210304228</v>
       </c>
       <c r="C3" t="n">
-        <v>26.45810062945154</v>
+        <v>28.85356502781376</v>
       </c>
       <c r="D3" t="n">
-        <v>80.89601082993718</v>
+        <v>65.95871950982196</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.28886447588937</v>
+        <v>41.61923042613503</v>
       </c>
       <c r="C4" t="n">
-        <v>90.94714382601602</v>
+        <v>117.4297881480737</v>
       </c>
       <c r="D4" t="n">
-        <v>184.6127470450915</v>
+        <v>144.9717382430137</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.092432819582</v>
+        <v>32.22586839190156</v>
       </c>
       <c r="C5" t="n">
-        <v>253.8063252404067</v>
+        <v>292.0208546282138</v>
       </c>
       <c r="D5" t="n">
-        <v>172.836683332651</v>
+        <v>135.6039016490907</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.54092728950677</v>
+        <v>17.63022527286423</v>
       </c>
       <c r="C6" t="n">
-        <v>257.9728624972302</v>
+        <v>302.8534587968731</v>
       </c>
       <c r="D6" t="n">
-        <v>91.25050386662829</v>
+        <v>72.65423885278521</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>147.5606069391126</v>
+        <v>206.1895980890279</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>74.85335371029805</v>
+        <v>106.2300103380261</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.444592841303563</v>
+        <v>7.182466204269665</v>
       </c>
       <c r="C2" t="n">
-        <v>4.718279466610171</v>
+        <v>11.23413897969625</v>
       </c>
       <c r="D2" t="n">
-        <v>16.81537467833937</v>
+        <v>15.0354660905399</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.55302705712722</v>
+        <v>13.02288329683394</v>
       </c>
       <c r="C3" t="n">
-        <v>8.546113765468485</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D3" t="n">
-        <v>15.50179625005713</v>
+        <v>8.374307917225293</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39779691281749</v>
+        <v>13.39790742398821</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14140736710331</v>
+        <v>70.14198592558532</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576211401507939</v>
+        <v>1.576224402822142</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.821362975556085</v>
+        <v>4.314781160164732</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>6.584581852383357</v>
       </c>
       <c r="D2" t="n">
-        <v>28.4392674966216</v>
+        <v>17.26305163147591</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.84250376115979</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="C3" t="n">
-        <v>14.71148934813846</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="D3" t="n">
-        <v>25.87886948394592</v>
+        <v>18.97718312309085</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.73643395137212</v>
+        <v>15.14934882423253</v>
       </c>
       <c r="C4" t="n">
-        <v>13.57953424514188</v>
+        <v>44.63123238276425</v>
       </c>
       <c r="D4" t="n">
-        <v>23.18986252201391</v>
+        <v>19.46314823669302</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44134406316341</v>
+        <v>15.43820357876427</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14644582606957</v>
+        <v>86.12892522889543</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250809276455455</v>
+        <v>3.250148121845111</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.322054304721958</v>
+        <v>5.495823648373645</v>
       </c>
       <c r="C2" t="n">
-        <v>7.590873249236338</v>
+        <v>6.293984531926301</v>
       </c>
       <c r="D2" t="n">
-        <v>36.66238626739288</v>
+        <v>24.98351557767283</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.50594422505237</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="C3" t="n">
-        <v>17.90216938694059</v>
+        <v>30.68943323475529</v>
       </c>
       <c r="D3" t="n">
-        <v>42.62257657987527</v>
+        <v>28.38232612977529</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.58398531977338</v>
+        <v>28.19284882285566</v>
       </c>
       <c r="C4" t="n">
-        <v>27.26117025152543</v>
+        <v>74.20245498238242</v>
       </c>
       <c r="D4" t="n">
-        <v>30.9495963763807</v>
+        <v>24.60652445924206</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.91627370769854</v>
+        <v>13.2045066221196</v>
       </c>
       <c r="C5" t="n">
-        <v>16.61607989437727</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73545392215792</v>
+        <v>16.72591015526634</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0862689251633</v>
+        <v>102.0280519471247</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020636176647375</v>
+        <v>4.181477538816585</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.46088164164826</v>
+        <v>5.217989048071797</v>
       </c>
       <c r="C2" t="n">
-        <v>6.617961274327748</v>
+        <v>6.430447462816608</v>
       </c>
       <c r="D2" t="n">
-        <v>34.31011876801753</v>
+        <v>29.6703791177471</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.35868206941536</v>
+        <v>18.09361018926871</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5633275602552</v>
+        <v>27.1011453757332</v>
       </c>
       <c r="D3" t="n">
-        <v>61.0058023418968</v>
+        <v>41.05668899160161</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.11925880276615</v>
+        <v>31.12827445855362</v>
       </c>
       <c r="C4" t="n">
-        <v>37.05017661057038</v>
+        <v>75.60635419945537</v>
       </c>
       <c r="D4" t="n">
-        <v>44.56741878198821</v>
+        <v>32.82571623919635</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.01064466049325</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>34.65569395991241</v>
+        <v>94.93500300066657</v>
       </c>
       <c r="D5" t="n">
-        <v>34.48388811166922</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.47801332097696</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64280806657019</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06113370083574</v>
+        <v>18.04043595897594</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8273960483093</v>
+        <v>117.6923679228431</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880431886032661</v>
+        <v>6.013478652991981</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.043458940894118</v>
+        <v>6.618943022031996</v>
       </c>
       <c r="C2" t="n">
-        <v>5.168901662859456</v>
+        <v>7.030295310111409</v>
       </c>
       <c r="D2" t="n">
-        <v>29.89814458513236</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>15.90922154731956</v>
       </c>
       <c r="C3" t="n">
-        <v>23.68957210347553</v>
+        <v>24.52405765208533</v>
       </c>
       <c r="D3" t="n">
-        <v>69.15921702566656</v>
+        <v>50.43237956715865</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.93835518327748</v>
+        <v>23.94286301117121</v>
       </c>
       <c r="C4" t="n">
-        <v>42.44880723622359</v>
+        <v>58.96376711706343</v>
       </c>
       <c r="D4" t="n">
-        <v>55.88795155965818</v>
+        <v>38.59446574935061</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.32279937271473</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C5" t="n">
-        <v>38.97538385859838</v>
+        <v>87.91550691530188</v>
       </c>
       <c r="D5" t="n">
-        <v>33.96847056693964</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.04782790006761</v>
+        <v>13.04153650321463</v>
       </c>
       <c r="C6" t="n">
-        <v>25.84156307118455</v>
+        <v>66.29447722467438</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>15.92983824910874</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059030379183952</v>
+        <v>7.045093536741643</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17840980484955</v>
+        <v>66.0477519069529</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294272784387964</v>
+        <v>4.403183460463526</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.891868883812609</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C2" t="n">
-        <v>4.95880765415064</v>
+        <v>8.339946747576654</v>
       </c>
       <c r="D2" t="n">
-        <v>24.11270536400591</v>
+        <v>24.03809253848315</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.35225180384213</v>
+        <v>20.40562603276996</v>
       </c>
       <c r="C3" t="n">
-        <v>21.4364611222291</v>
+        <v>26.37956081311179</v>
       </c>
       <c r="D3" t="n">
-        <v>77.56297737401925</v>
+        <v>62.42442777453343</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.81746134693488</v>
+        <v>28.16732338254523</v>
       </c>
       <c r="C4" t="n">
-        <v>53.14396672628834</v>
+        <v>60.58463257677491</v>
       </c>
       <c r="D4" t="n">
-        <v>78.63111887623978</v>
+        <v>56.06662964183109</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>30.50780990946964</v>
       </c>
       <c r="C5" t="n">
-        <v>62.75822199397737</v>
+        <v>100.7518581483289</v>
       </c>
       <c r="D5" t="n">
-        <v>47.73748211900116</v>
+        <v>36.61918936840603</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.15728492132452</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>47.41645061971246</v>
+        <v>108.8404774836184</v>
       </c>
       <c r="D6" t="n">
-        <v>35.54221213684728</v>
+        <v>33.24786775202249</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.15698182168825</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>28.68568617038755</v>
+        <v>66.65379688442869</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>20.5283444958008</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281530076638342</v>
+        <v>7.261286595273818</v>
       </c>
       <c r="C21" t="n">
-        <v>75.5458745451228</v>
+        <v>75.33584842596586</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371338817058549</v>
+        <v>5.445964946455363</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.373506095970292</v>
+        <v>4.816454237034852</v>
       </c>
       <c r="C2" t="n">
-        <v>9.935286766977722</v>
+        <v>7.760715602071037</v>
       </c>
       <c r="D2" t="n">
-        <v>20.42722448226338</v>
+        <v>26.62990647769473</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.08717992369549</v>
+        <v>19.29134238844982</v>
       </c>
       <c r="C3" t="n">
-        <v>20.13564541410208</v>
+        <v>29.90403507135785</v>
       </c>
       <c r="D3" t="n">
-        <v>78.85397560510381</v>
+        <v>66.80793127399544</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.5216364927871</v>
+        <v>34.65078522139117</v>
       </c>
       <c r="C4" t="n">
-        <v>53.50132289063419</v>
+        <v>63.6987362946458</v>
       </c>
       <c r="D4" t="n">
-        <v>99.85552249435158</v>
+        <v>73.19420009012096</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>36.71736413883072</v>
       </c>
       <c r="C5" t="n">
-        <v>82.41771977151974</v>
+        <v>106.0042083660494</v>
       </c>
       <c r="D5" t="n">
-        <v>64.69717370986481</v>
+        <v>48.47379289718628</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.09944392223197</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="C6" t="n">
-        <v>76.67940444019713</v>
+        <v>136.8153783161313</v>
       </c>
       <c r="D6" t="n">
-        <v>42.82776185006286</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>50.783845245279</v>
+        <v>115.1619509512636</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>30.37527396939631</v>
+        <v>59.91606239018283</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>24.96093538047515</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.492140745508865</v>
+        <v>7.463737232242657</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22310098016334</v>
+        <v>83.96704386272989</v>
       </c>
       <c r="D21" t="n">
-        <v>7.492140745508865</v>
+        <v>6.530770078212325</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497618605175</v>
+        <v>10.84497622349837</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907143260677</v>
+        <v>37.78907156308868</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.429465715112362</v>
+        <v>5.698063675448488</v>
       </c>
       <c r="C2" t="n">
-        <v>9.02422489743668</v>
+        <v>10.10218387669968</v>
       </c>
       <c r="D2" t="n">
-        <v>23.36068662255285</v>
+        <v>37.9838186773091</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.67636741496382</v>
+        <v>16.54735755507999</v>
       </c>
       <c r="C3" t="n">
-        <v>30.2280118137593</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7608484419206</v>
+        <v>90.77730147318132</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.91429451675682</v>
+        <v>31.31971526088175</v>
       </c>
       <c r="C4" t="n">
-        <v>68.7655361962636</v>
+        <v>106.4666115347496</v>
       </c>
       <c r="D4" t="n">
-        <v>88.33078619419827</v>
+        <v>108.4958840394278</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.85957868722626</v>
+        <v>39.88350048502668</v>
       </c>
       <c r="C5" t="n">
-        <v>111.8701508989241</v>
+        <v>136.4629308903067</v>
       </c>
       <c r="D5" t="n">
-        <v>61.5801247488812</v>
+        <v>79.17795234750527</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>38.88309957439917</v>
       </c>
       <c r="C6" t="n">
-        <v>151.4669810543107</v>
+        <v>108.2769543013807</v>
       </c>
       <c r="D6" t="n">
-        <v>43.47178834404877</v>
+        <v>52.81017250684443</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.16477905005999</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>156.663371652889</v>
+        <v>89.11127561907448</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>104.5610392408065</v>
+        <v>62.0022762617073</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14062057254808</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.650896095638282</v>
+        <v>7.678847570440854</v>
       </c>
       <c r="C21" t="n">
-        <v>92.76711515961416</v>
+        <v>94.06588273790045</v>
       </c>
       <c r="D21" t="n">
-        <v>7.650896095638282</v>
+        <v>7.678847570440854</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.730862260316131</v>
+        <v>5.912084674974292</v>
       </c>
       <c r="C2" t="n">
-        <v>13.78079252451248</v>
+        <v>18.27621526225862</v>
       </c>
       <c r="D2" t="n">
-        <v>28.57671217521616</v>
+        <v>39.29936060099982</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32079481957723</v>
+        <v>17.57328390601791</v>
       </c>
       <c r="C3" t="n">
-        <v>32.41240045570844</v>
+        <v>39.5987936507951</v>
       </c>
       <c r="D3" t="n">
-        <v>72.81622722398593</v>
+        <v>97.51209072431445</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.31895449735575</v>
+        <v>30.93683365622549</v>
       </c>
       <c r="C4" t="n">
-        <v>71.85411447382405</v>
+        <v>102.6505582083422</v>
       </c>
       <c r="D4" t="n">
-        <v>99.88104793466199</v>
+        <v>123.7345719047467</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.47379289718628</v>
+        <v>42.85328729037328</v>
       </c>
       <c r="C5" t="n">
-        <v>117.4415691205247</v>
+        <v>164.4181967687346</v>
       </c>
       <c r="D5" t="n">
-        <v>76.33088400518952</v>
+        <v>96.65306148309851</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.7850069194325</v>
+        <v>45.92713935237005</v>
       </c>
       <c r="C6" t="n">
-        <v>162.375179796197</v>
+        <v>156.0959214798344</v>
       </c>
       <c r="D6" t="n">
-        <v>50.71708640139023</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.78845088416398</v>
+        <v>35.69241953559704</v>
       </c>
       <c r="C7" t="n">
-        <v>186.1874703627033</v>
+        <v>119.2342404284794</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.19731559302038</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C8" t="n">
-        <v>150.290847304623</v>
+        <v>88.12167393319369</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>86.97499261463339</v>
+        <v>54.91405783704532</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.822323088722336</v>
+        <v>7.852416731467463</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7124097673001</v>
+        <v>102.081417509077</v>
       </c>
       <c r="D21" t="n">
-        <v>8.800113474812628</v>
+        <v>8.833968822900896</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.211918635397069</v>
+        <v>6.740679737358599</v>
       </c>
       <c r="C2" t="n">
-        <v>14.00757624419349</v>
+        <v>15.19647271403638</v>
       </c>
       <c r="D2" t="n">
-        <v>26.04282135055514</v>
+        <v>49.72944821091794</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2240027074843</v>
+        <v>18.09361018926871</v>
       </c>
       <c r="C3" t="n">
-        <v>41.43466185773664</v>
+        <v>53.10273332270997</v>
       </c>
       <c r="D3" t="n">
-        <v>76.56159471568751</v>
+        <v>103.1473225466911</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.40829353844221</v>
+        <v>31.14103717870883</v>
       </c>
       <c r="C4" t="n">
-        <v>74.78954010952202</v>
+        <v>99.65131897186825</v>
       </c>
       <c r="D4" t="n">
-        <v>109.7211051743278</v>
+        <v>138.6541917661855</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.23464736797755</v>
+        <v>43.85957868722626</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2275891787279</v>
+        <v>172.7139648696201</v>
       </c>
       <c r="D5" t="n">
-        <v>88.82362354173019</v>
+        <v>111.7719761284994</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.14476854754334</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="C6" t="n">
-        <v>172.840610323468</v>
+        <v>197.8771402771702</v>
       </c>
       <c r="D6" t="n">
-        <v>60.0554705641859</v>
+        <v>74.7070733023653</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.87314322863646</v>
+        <v>43.23813239043802</v>
       </c>
       <c r="C7" t="n">
-        <v>205.4110721595601</v>
+        <v>163.4305585782623</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>50.72395863531995</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.87458264023044</v>
+        <v>28.28906009787184</v>
       </c>
       <c r="C8" t="n">
-        <v>189.3447709795611</v>
+        <v>116.2438369213436</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>126.9124892233936</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>68.32964021557801</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.977247160369577</v>
+        <v>8.007924161505525</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6928366649893</v>
+        <v>109.1079667005128</v>
       </c>
       <c r="D21" t="n">
-        <v>9.971558950461972</v>
+        <v>10.00990520188191</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.707300315414209</v>
+        <v>6.262568605390403</v>
       </c>
       <c r="C2" t="n">
-        <v>9.748754703170826</v>
+        <v>10.69810473317749</v>
       </c>
       <c r="D2" t="n">
-        <v>21.56899706230243</v>
+        <v>40.77296390507428</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.85156047467626</v>
+        <v>21.30392518215579</v>
       </c>
       <c r="C3" t="n">
-        <v>59.48409340031424</v>
+        <v>74.82881001769189</v>
       </c>
       <c r="D3" t="n">
-        <v>82.78587516061229</v>
+        <v>110.4515254662874</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.64932044760141</v>
+        <v>21.07125097624929</v>
       </c>
       <c r="C4" t="n">
-        <v>100.493658502112</v>
+        <v>138.8328698483585</v>
       </c>
       <c r="D4" t="n">
-        <v>103.5439486192068</v>
+        <v>131.2390513560094</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.04777114680538</v>
+        <v>28.42159603794517</v>
       </c>
       <c r="C5" t="n">
-        <v>103.2798584867645</v>
+        <v>118.2269672839222</v>
       </c>
       <c r="D5" t="n">
-        <v>59.73934780341843</v>
+        <v>73.60653412590462</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.45792070300229</v>
+        <v>26.84785446803753</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2858153929147</v>
+        <v>107.6329278073948</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>133.1279339389802</v>
+        <v>81.74522259411066</v>
       </c>
       <c r="D7" t="n">
-        <v>27.5478405811655</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>93.54582999915733</v>
+        <v>56.66156875060466</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14062057254808</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.023202092003429</v>
+        <v>3.787582642984194</v>
       </c>
       <c r="C2" t="n">
-        <v>5.237624002156734</v>
+        <v>4.725151700539898</v>
       </c>
       <c r="D2" t="n">
-        <v>15.16800203061322</v>
+        <v>28.99395494952105</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.07736244665303</v>
+        <v>22.10895829963817</v>
       </c>
       <c r="C3" t="n">
-        <v>49.75988238974958</v>
+        <v>59.75898275750335</v>
       </c>
       <c r="D3" t="n">
-        <v>82.21646149214914</v>
+        <v>116.2192932287374</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.7491399182651</v>
+        <v>28.92032387170254</v>
       </c>
       <c r="C4" t="n">
-        <v>126.6955229807551</v>
+        <v>164.5497509611036</v>
       </c>
       <c r="D4" t="n">
-        <v>118.4635684806456</v>
+        <v>152.2209632911722</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.53297549688156</v>
+        <v>31.04777114680538</v>
       </c>
       <c r="C5" t="n">
-        <v>141.4943878745716</v>
+        <v>179.9788978810465</v>
       </c>
       <c r="D5" t="n">
-        <v>75.103699374881</v>
+        <v>93.36420667387168</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>31.47679489356124</v>
       </c>
       <c r="C6" t="n">
-        <v>153.3588088803943</v>
+        <v>141.3235637740326</v>
       </c>
       <c r="D6" t="n">
-        <v>36.06548366321083</v>
+        <v>41.49945720621693</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>162.1729397691221</v>
+        <v>108.8738569055628</v>
       </c>
       <c r="D7" t="n">
-        <v>29.88341836956866</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4997132192535</v>
+        <v>73.60162538738336</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>29.31989518733098</v>
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.112541133089889</v>
+        <v>3.729659528433633</v>
       </c>
       <c r="C2" t="n">
-        <v>9.032078879070655</v>
+        <v>3.903428872085318</v>
       </c>
       <c r="D2" t="n">
-        <v>16.67694825204057</v>
+        <v>25.28785736598934</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.90355204527233</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="C3" t="n">
-        <v>34.83731728519807</v>
+        <v>39.08828484458675</v>
       </c>
       <c r="D3" t="n">
-        <v>75.82037519898117</v>
+        <v>113.4311297486765</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>34.61249706092554</v>
       </c>
       <c r="C4" t="n">
-        <v>125.3171492039926</v>
+        <v>156.8921188679785</v>
       </c>
       <c r="D4" t="n">
-        <v>130.4094745459208</v>
+        <v>170.6248057549829</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.88979188187966</v>
+        <v>36.44738352016284</v>
       </c>
       <c r="C5" t="n">
-        <v>184.6176557836127</v>
+        <v>236.4784782604505</v>
       </c>
       <c r="D5" t="n">
-        <v>96.26036240139979</v>
+        <v>118.3251420543468</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.16486116551801</v>
+        <v>36.34724525432967</v>
       </c>
       <c r="C6" t="n">
-        <v>187.4117097498991</v>
+        <v>206.3702396666093</v>
       </c>
       <c r="D6" t="n">
-        <v>48.10072876957248</v>
+        <v>56.99634471775284</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>189.2416874706151</v>
+        <v>149.5368650677614</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>162.9750276434918</v>
+        <v>104.1437964665016</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>94.85155444580556</v>
+        <v>61.4593697812588</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.496584411899639</v>
+        <v>2.284526907782328</v>
       </c>
       <c r="C2" t="n">
-        <v>4.364850293081319</v>
+        <v>1.948769192929919</v>
       </c>
       <c r="D2" t="n">
-        <v>11.62978330450772</v>
+        <v>17.88253443285565</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>37.18860303686917</v>
+        <v>31.98043146583985</v>
       </c>
       <c r="D3" t="n">
-        <v>74.90734983403163</v>
+        <v>112.3168461043563</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.48709539668921</v>
+        <v>37.79041437957247</v>
       </c>
       <c r="C4" t="n">
-        <v>124.0664026287822</v>
+        <v>152.2337260113274</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9477343297553</v>
+        <v>184.3447299218321</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>37.79728661350221</v>
       </c>
       <c r="C5" t="n">
-        <v>224.2311756499715</v>
+        <v>287.3575530330414</v>
       </c>
       <c r="D5" t="n">
-        <v>101.8563243156066</v>
+        <v>121.6876279413922</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>29.42396044398116</v>
       </c>
       <c r="C6" t="n">
-        <v>224.8054980569559</v>
+        <v>227.9451272151372</v>
       </c>
       <c r="D6" t="n">
-        <v>47.33594730796422</v>
+        <v>55.18502020341747</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>202.5964014914845</v>
+        <v>147.979813208826</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>117.8293594637022</v>
+        <v>73.8519710519663</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.119994204096364</v>
+        <v>3.033600406122644</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9248473951295</v>
+        <v>11.52473630015331</v>
       </c>
       <c r="D2" t="n">
-        <v>13.39202043363074</v>
+        <v>15.3437348696734</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.82300767579509</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C3" t="n">
-        <v>27.29749491658256</v>
+        <v>20.238728923048</v>
       </c>
       <c r="D3" t="n">
-        <v>67.84367510197583</v>
+        <v>103.0933264229576</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.55166976099125</v>
+        <v>35.27615850899639</v>
       </c>
       <c r="C4" t="n">
-        <v>109.121257327033</v>
+        <v>120.0206203395811</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2870591825262</v>
+        <v>194.2358380421187</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.00179323562181</v>
+        <v>45.20948178056562</v>
       </c>
       <c r="C5" t="n">
-        <v>227.9127295408971</v>
+        <v>283.6023680642974</v>
       </c>
       <c r="D5" t="n">
-        <v>122.5466571826081</v>
+        <v>149.2747384307276</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.89568236810514</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C6" t="n">
-        <v>282.6471275480652</v>
+        <v>326.1994192038622</v>
       </c>
       <c r="D6" t="n">
-        <v>63.23535137824131</v>
+        <v>72.49323222928874</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>256.8536701143888</v>
+        <v>218.6460129605114</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>176.4936935309703</v>
+        <v>119.3314334511998</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>50.47655821384974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3103,7 +3103,7 @@
         <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.175552912610932</v>
+        <v>1.942878706704438</v>
       </c>
       <c r="C2" t="n">
-        <v>4.466952054322987</v>
+        <v>6.271404334728625</v>
       </c>
       <c r="D2" t="n">
-        <v>10.70890395792421</v>
+        <v>11.45405046544754</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59582304548658</v>
+        <v>11.86932974434394</v>
       </c>
       <c r="C3" t="n">
-        <v>25.91323065359456</v>
+        <v>30.94468763785946</v>
       </c>
       <c r="D3" t="n">
-        <v>64.16212121105029</v>
+        <v>95.68113125589414</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.18681946790993</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>94.29097650668065</v>
+        <v>95.23541779816608</v>
       </c>
       <c r="D4" t="n">
-        <v>144.435703996495</v>
+        <v>198.6900273762865</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.54237636776331</v>
+        <v>48.57196766761096</v>
       </c>
       <c r="C5" t="n">
-        <v>225.6792535137356</v>
+        <v>271.3550654538184</v>
       </c>
       <c r="D5" t="n">
-        <v>137.3219601315226</v>
+        <v>167.6825078853552</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.33594730796422</v>
+        <v>42.30449032369931</v>
       </c>
       <c r="C6" t="n">
-        <v>320.9264522843526</v>
+        <v>377.5605320992384</v>
       </c>
       <c r="D6" t="n">
-        <v>74.3045567436241</v>
+        <v>86.98382834397167</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>13.83380690054181</v>
       </c>
       <c r="C7" t="n">
-        <v>311.230711957211</v>
+        <v>286.257995604285</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>220.0538391684013</v>
+        <v>157.5508715775281</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>79.43124325520091</v>
+        <v>52.58437053486764</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.029673415305656</v>
+        <v>2.438661297349077</v>
       </c>
       <c r="C2" t="n">
-        <v>8.829838851995813</v>
+        <v>12.02640937702343</v>
       </c>
       <c r="D2" t="n">
-        <v>18.31057643190726</v>
+        <v>14.41794678456866</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.12672756930585</v>
+        <v>9.439504176333081</v>
       </c>
       <c r="C3" t="n">
-        <v>21.93224371287374</v>
+        <v>28.10743677258618</v>
       </c>
       <c r="D3" t="n">
-        <v>58.96867585558466</v>
+        <v>85.40714153095126</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.86476516318797</v>
+        <v>27.50366193447439</v>
       </c>
       <c r="C4" t="n">
-        <v>81.46444275069608</v>
+        <v>87.57778570504097</v>
       </c>
       <c r="D4" t="n">
-        <v>143.0445674995773</v>
+        <v>199.3792142646677</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.87969666739671</v>
+        <v>48.03200643027521</v>
       </c>
       <c r="C5" t="n">
-        <v>203.9335418646687</v>
+        <v>230.9070600388499</v>
       </c>
       <c r="D5" t="n">
-        <v>149.3483695085461</v>
+        <v>189.3300447639974</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.31206656789281</v>
+        <v>49.91205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>336.3025848282662</v>
+        <v>402.2750488059476</v>
       </c>
       <c r="D6" t="n">
-        <v>92.17629195173305</v>
+        <v>107.5121728397725</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.44613973055133</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>369.7399298872082</v>
+        <v>377.8845088416398</v>
       </c>
       <c r="D7" t="n">
-        <v>48.98724694650735</v>
+        <v>53.29908286355933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>293.2382217814798</v>
+        <v>233.1552622815749</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>144.1078002632765</v>
+        <v>99.17811657842124</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.95899724726245</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.130032665317084</v>
+        <v>4.845906668162256</v>
       </c>
       <c r="C2" t="n">
-        <v>11.48153940116645</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="D2" t="n">
-        <v>6.23900666048848</v>
+        <v>17.45841942462103</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.213841073076558</v>
+        <v>1.820160243673586</v>
       </c>
       <c r="C2" t="n">
-        <v>5.226824777410018</v>
+        <v>7.312056901230244</v>
       </c>
       <c r="D2" t="n">
-        <v>13.62273114412874</v>
+        <v>10.84143989799753</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.53339210304228</v>
+        <v>12.41910845872215</v>
       </c>
       <c r="C3" t="n">
-        <v>28.85356502781376</v>
+        <v>37.87582642984194</v>
       </c>
       <c r="D3" t="n">
-        <v>65.95871950982196</v>
+        <v>91.33689766460201</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.61923042613503</v>
+        <v>36.89702396870788</v>
       </c>
       <c r="C4" t="n">
-        <v>117.4297881480737</v>
+        <v>127.2570826675843</v>
       </c>
       <c r="D4" t="n">
-        <v>144.9717382430137</v>
+        <v>200.6554862801886</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.22586839190156</v>
+        <v>28.10252803406495</v>
       </c>
       <c r="C5" t="n">
-        <v>292.0208546282138</v>
+        <v>343.7835023346269</v>
       </c>
       <c r="D5" t="n">
-        <v>135.6039016490907</v>
+        <v>167.2407214184442</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.63022527286423</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>302.8534587968731</v>
+        <v>311.950333024424</v>
       </c>
       <c r="D6" t="n">
-        <v>72.65423885278521</v>
+        <v>82.51589454194442</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>206.1895980890279</v>
+        <v>163.9695380678938</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>73.1009340582175</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>20.21418523044183</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.81497376771187</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>18.12993485432585</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.182466204269665</v>
+        <v>7.059747741238813</v>
       </c>
       <c r="C2" t="n">
-        <v>11.23413897969625</v>
+        <v>6.369579105153306</v>
       </c>
       <c r="D2" t="n">
-        <v>15.0354660905399</v>
+        <v>19.51910785583508</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.02288329683394</v>
+        <v>10.29853341754904</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9321048441535</v>
+        <v>13.4204911170539</v>
       </c>
       <c r="D3" t="n">
-        <v>8.374307917225293</v>
+        <v>17.79908587799467</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39790742398821</v>
+        <v>13.39725927996997</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14198592558532</v>
+        <v>70.13859270101928</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576224402822142</v>
+        <v>1.576148150584703</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.314781160164732</v>
+        <v>4.458116324984766</v>
       </c>
       <c r="C2" t="n">
-        <v>6.584581852383357</v>
+        <v>3.757148464152543</v>
       </c>
       <c r="D2" t="n">
-        <v>17.26305163147591</v>
+        <v>27.52722387937632</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>18.6973850273805</v>
       </c>
       <c r="C3" t="n">
-        <v>38.23907308041327</v>
+        <v>20.56270566544944</v>
       </c>
       <c r="D3" t="n">
-        <v>18.97718312309085</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.14934882423253</v>
+        <v>12.06077054667207</v>
       </c>
       <c r="C4" t="n">
-        <v>44.63123238276425</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D4" t="n">
-        <v>19.46314823669302</v>
+        <v>24.40232093675872</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43820357876427</v>
+        <v>15.43924748411346</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12892522889543</v>
+        <v>86.13474912189615</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250148121845111</v>
+        <v>3.250367891392307</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.495823648373645</v>
+        <v>4.643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>6.293984531926301</v>
+        <v>4.636794407157685</v>
       </c>
       <c r="D2" t="n">
-        <v>24.98351557767283</v>
+        <v>21.00154688924777</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35239067256238</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="C3" t="n">
-        <v>30.68943323475529</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="D3" t="n">
-        <v>28.38232612977529</v>
+        <v>44.97877107006762</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.19284882285566</v>
+        <v>25.72964383290041</v>
       </c>
       <c r="C4" t="n">
-        <v>74.20245498238242</v>
+        <v>38.95182191369645</v>
       </c>
       <c r="D4" t="n">
-        <v>24.60652445924206</v>
+        <v>33.89778473223387</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.2045066221196</v>
+        <v>10.79922474671492</v>
       </c>
       <c r="C5" t="n">
-        <v>48.49833658979244</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>31.41592653589794</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72591015526634</v>
+        <v>16.7313147224126</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0280519471247</v>
+        <v>102.0610198067169</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181477538816585</v>
+        <v>4.18282868060315</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.217989048071797</v>
+        <v>4.481678269886689</v>
       </c>
       <c r="C2" t="n">
-        <v>6.430447462816608</v>
+        <v>10.78351678344696</v>
       </c>
       <c r="D2" t="n">
-        <v>29.6703791177471</v>
+        <v>25.27705814124263</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09361018926871</v>
+        <v>16.34119053718816</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1011453757332</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="D3" t="n">
-        <v>41.05668899160161</v>
+        <v>50.93307089632452</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.12827445855362</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="C4" t="n">
-        <v>75.60635419945537</v>
+        <v>40.90451809744336</v>
       </c>
       <c r="D4" t="n">
-        <v>32.82571623919635</v>
+        <v>48.01335322389451</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.26804248545517</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>94.93500300066657</v>
+        <v>49.84823968313181</v>
       </c>
       <c r="D5" t="n">
-        <v>31.51410130632262</v>
+        <v>35.9810533606456</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.79373517111693</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>45.68562941712533</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
         <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04043595897594</v>
+        <v>18.05768348922439</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6923679228431</v>
+        <v>117.8048875249401</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013478652991981</v>
+        <v>6.019227829741463</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.618943022031996</v>
+        <v>5.627377840742716</v>
       </c>
       <c r="C2" t="n">
-        <v>7.030295310111409</v>
+        <v>15.95241844630642</v>
       </c>
       <c r="D2" t="n">
-        <v>28.78680618392497</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>14.04390090925062</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52405765208533</v>
+        <v>29.59969328304133</v>
       </c>
       <c r="D3" t="n">
-        <v>50.43237956715865</v>
+        <v>55.33620934987147</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.94286301117121</v>
+        <v>22.23265851037327</v>
       </c>
       <c r="C4" t="n">
-        <v>58.96376711706343</v>
+        <v>35.32720938961722</v>
       </c>
       <c r="D4" t="n">
-        <v>38.59446574935061</v>
+        <v>54.03735713715294</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.67837196810132</v>
+        <v>21.30392518215579</v>
       </c>
       <c r="C5" t="n">
-        <v>87.91550691530188</v>
+        <v>47.5411325781518</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>35.85833489761475</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.04153650321463</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="C6" t="n">
-        <v>66.29447722467438</v>
+        <v>36.50825187782615</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>27.84727363096077</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045093536741643</v>
+        <v>7.058214634336861</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0477519069529</v>
+        <v>66.17076219690807</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403183460463526</v>
+        <v>4.411384146460538</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.340707511102648</v>
+        <v>4.705516746454962</v>
       </c>
       <c r="C2" t="n">
-        <v>8.339946747576654</v>
+        <v>11.15461741565226</v>
       </c>
       <c r="D2" t="n">
-        <v>24.03809253848315</v>
+        <v>39.85012106308228</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.40562603276996</v>
+        <v>17.55364895193297</v>
       </c>
       <c r="C3" t="n">
-        <v>26.37956081311179</v>
+        <v>50.71217766286899</v>
       </c>
       <c r="D3" t="n">
-        <v>62.42442777453343</v>
+        <v>69.5813685384927</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.16732338254523</v>
+        <v>25.76793199336603</v>
       </c>
       <c r="C4" t="n">
-        <v>60.58463257677491</v>
+        <v>59.76781848684157</v>
       </c>
       <c r="D4" t="n">
-        <v>56.06662964183109</v>
+        <v>69.9779946110084</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.50780990946964</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>100.7518581483289</v>
+        <v>58.48761948050374</v>
       </c>
       <c r="D5" t="n">
-        <v>36.61918936840603</v>
+        <v>48.47379289718628</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.86294053649972</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8404774836184</v>
+        <v>59.16993413495527</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>66.65379688442869</v>
+        <v>39.04606969330414</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>28.95664853675967</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261286595273818</v>
+        <v>7.280241165549317</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33584842596586</v>
+        <v>75.53250209257416</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445964946455363</v>
+        <v>5.460180874161987</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.816454237034852</v>
+        <v>4.730060439061132</v>
       </c>
       <c r="C2" t="n">
-        <v>7.760715602071037</v>
+        <v>9.232355410737005</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62990647769473</v>
+        <v>32.80509953740717</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29134238844982</v>
+        <v>16.84679060487527</v>
       </c>
       <c r="C3" t="n">
-        <v>29.90403507135785</v>
+        <v>46.32376542488575</v>
       </c>
       <c r="D3" t="n">
-        <v>66.80793127399544</v>
+        <v>85.31387549904782</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.65078522139117</v>
+        <v>30.68157925312132</v>
       </c>
       <c r="C4" t="n">
-        <v>63.6987362946458</v>
+        <v>98.0815043927776</v>
       </c>
       <c r="D4" t="n">
-        <v>73.19420009012096</v>
+        <v>89.14760028413161</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.71736413883072</v>
+        <v>34.09118902997049</v>
       </c>
       <c r="C5" t="n">
-        <v>106.0042083660494</v>
+        <v>88.13640014875742</v>
       </c>
       <c r="D5" t="n">
-        <v>48.47379289718628</v>
+        <v>62.21826075664162</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.80509953740717</v>
+        <v>31.03402667894593</v>
       </c>
       <c r="C6" t="n">
-        <v>136.8153783161313</v>
+        <v>77.88695411642071</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>43.9548082145382</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>115.1619509512636</v>
+        <v>64.43799231594365</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>59.91606239018283</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.463737232242657</v>
+        <v>7.487625199765883</v>
       </c>
       <c r="C21" t="n">
-        <v>83.96704386272989</v>
+        <v>85.17173664733691</v>
       </c>
       <c r="D21" t="n">
-        <v>6.530770078212325</v>
+        <v>6.551672049795148</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_97_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622349837</v>
+        <v>10.84497639903954</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907156308868</v>
+        <v>37.78907217475788</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.698063675448488</v>
+        <v>1.61890196430299</v>
       </c>
       <c r="C2" t="n">
-        <v>10.10218387669968</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="D2" t="n">
-        <v>37.9838186773091</v>
+        <v>14.75468624712531</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54735755507999</v>
+        <v>13.06215320500381</v>
       </c>
       <c r="C3" t="n">
-        <v>40.47254910757476</v>
+        <v>30.33600406122644</v>
       </c>
       <c r="D3" t="n">
-        <v>90.77730147318132</v>
+        <v>72.49715922010571</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.31971526088175</v>
+        <v>21.60728522276805</v>
       </c>
       <c r="C4" t="n">
-        <v>106.4666115347496</v>
+        <v>85.91863208486386</v>
       </c>
       <c r="D4" t="n">
-        <v>108.4958840394278</v>
+        <v>82.3961213220263</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.88350048502668</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="C5" t="n">
-        <v>136.4629308903067</v>
+        <v>94.1741485298753</v>
       </c>
       <c r="D5" t="n">
-        <v>79.17795234750527</v>
+        <v>51.02633692822798</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.88309957439917</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>108.2769543013807</v>
+        <v>62.55107322838128</v>
       </c>
       <c r="D6" t="n">
-        <v>52.81017250684443</v>
+        <v>29.98748362621883</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>89.11127561907448</v>
+        <v>36.05173919535137</v>
       </c>
       <c r="D7" t="n">
-        <v>40.42346172236242</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>62.0022762617073</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.678847570440854</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.06588273790045</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.678847570440854</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.912084674974292</v>
+        <v>2.222676802414779</v>
       </c>
       <c r="C2" t="n">
-        <v>18.27621526225862</v>
+        <v>12.0195371430937</v>
       </c>
       <c r="D2" t="n">
-        <v>39.29936060099982</v>
+        <v>16.27443169329938</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.57328390601791</v>
+        <v>9.002626447943252</v>
       </c>
       <c r="C3" t="n">
-        <v>39.5987936507951</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D3" t="n">
-        <v>97.51209072431445</v>
+        <v>68.17746932141975</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.93683365622549</v>
+        <v>23.90457485070559</v>
       </c>
       <c r="C4" t="n">
-        <v>102.6505582083422</v>
+        <v>81.030510265419</v>
       </c>
       <c r="D4" t="n">
-        <v>123.7345719047467</v>
+        <v>99.24291192690157</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.85328729037328</v>
+        <v>26.94897448157495</v>
       </c>
       <c r="C5" t="n">
-        <v>164.4181967687346</v>
+        <v>129.7134154236099</v>
       </c>
       <c r="D5" t="n">
-        <v>96.65306148309851</v>
+        <v>68.03511590430396</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.92713935237005</v>
+        <v>20.64909946342317</v>
       </c>
       <c r="C6" t="n">
-        <v>156.0959214798344</v>
+        <v>109.2027423864855</v>
       </c>
       <c r="D6" t="n">
-        <v>62.67182819600364</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.69241953559704</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="C7" t="n">
-        <v>119.2342404284794</v>
+        <v>64.31821909602553</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>88.12167393319369</v>
+        <v>39.05392367493811</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.852416731467463</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.081417509077</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.833968822900896</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.740679737358599</v>
+        <v>1.161407534123977</v>
       </c>
       <c r="C2" t="n">
-        <v>15.19647271403638</v>
+        <v>4.94309969088269</v>
       </c>
       <c r="D2" t="n">
-        <v>49.72944821091794</v>
+        <v>10.99753778297277</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09361018926871</v>
+        <v>9.24315463548372</v>
       </c>
       <c r="C3" t="n">
-        <v>53.10273332270997</v>
+        <v>33.77702976461151</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1473225466911</v>
+        <v>68.01057221169779</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.14103717870883</v>
+        <v>26.29120351972959</v>
       </c>
       <c r="C4" t="n">
-        <v>99.65131897186825</v>
+        <v>74.4704721056418</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6541917661855</v>
+        <v>109.9763595774319</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.85957868722626</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="C5" t="n">
-        <v>172.7139648696201</v>
+        <v>152.9562923216531</v>
       </c>
       <c r="D5" t="n">
-        <v>111.7719761284994</v>
+        <v>78.34346679889548</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>15.81890075852886</v>
       </c>
       <c r="C6" t="n">
-        <v>197.8771402771702</v>
+        <v>142.5311134502562</v>
       </c>
       <c r="D6" t="n">
-        <v>74.7070733023653</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.23813239043802</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>163.4305585782623</v>
+        <v>63.89901282631214</v>
       </c>
       <c r="D7" t="n">
-        <v>50.72395863531995</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.28906009787184</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>116.2438369213436</v>
+        <v>39.63806355896497</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.007924161505525</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1079667005128</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00990520188191</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.262568605390403</v>
+        <v>1.054397034361074</v>
       </c>
       <c r="C2" t="n">
-        <v>10.69810473317749</v>
+        <v>4.232314353007999</v>
       </c>
       <c r="D2" t="n">
-        <v>40.77296390507428</v>
+        <v>12.86089492563322</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.30392518215579</v>
+        <v>6.464808632465247</v>
       </c>
       <c r="C3" t="n">
-        <v>74.82881001769189</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D3" t="n">
-        <v>110.4515254662874</v>
+        <v>61.24142179091603</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.07125097624929</v>
+        <v>22.4240993127014</v>
       </c>
       <c r="C4" t="n">
-        <v>138.8328698483585</v>
+        <v>80.80078130262524</v>
       </c>
       <c r="D4" t="n">
-        <v>131.2390513560094</v>
+        <v>119.8802304178738</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.42159603794517</v>
+        <v>33.67394625566561</v>
       </c>
       <c r="C5" t="n">
-        <v>118.2269672839222</v>
+        <v>146.2804079327748</v>
       </c>
       <c r="D5" t="n">
-        <v>73.60653412590462</v>
+        <v>97.68389657255766</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.84785446803753</v>
+        <v>24.83527167433157</v>
       </c>
       <c r="C6" t="n">
-        <v>107.6329278073948</v>
+        <v>195.8243058275901</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>52.16614601285853</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>81.74522259411066</v>
+        <v>131.8703151298401</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>56.66156875060466</v>
+        <v>61.08434215823654</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.787582642984194</v>
+        <v>0.6842781498600269</v>
       </c>
       <c r="C2" t="n">
-        <v>4.725151700539898</v>
+        <v>2.118611545764617</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99395494952105</v>
+        <v>10.13163630782708</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.10895829963817</v>
+        <v>5.252350217720436</v>
       </c>
       <c r="C3" t="n">
-        <v>59.75898275750335</v>
+        <v>21.13211933391259</v>
       </c>
       <c r="D3" t="n">
-        <v>116.2192932287374</v>
+        <v>58.12928156845365</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.92032387170254</v>
+        <v>18.90158854986384</v>
       </c>
       <c r="C4" t="n">
-        <v>164.5497509611036</v>
+        <v>74.66191290796993</v>
       </c>
       <c r="D4" t="n">
-        <v>152.2209632911722</v>
+        <v>123.4282666210217</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.04777114680538</v>
+        <v>35.78470381979624</v>
       </c>
       <c r="C5" t="n">
-        <v>179.9788978810465</v>
+        <v>152.6863117029852</v>
       </c>
       <c r="D5" t="n">
-        <v>93.36420667387168</v>
+        <v>114.4226949299658</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.47679489356124</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>141.3235637740326</v>
+        <v>221.8268755222711</v>
       </c>
       <c r="D6" t="n">
-        <v>41.49945720621693</v>
+        <v>64.44290105446488</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>11.07902284242525</v>
       </c>
       <c r="C7" t="n">
-        <v>108.8738569055628</v>
+        <v>187.7445222216388</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>91.6265132373548</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>48.14687091167205</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.729659528433633</v>
+        <v>0.8246680715673208</v>
       </c>
       <c r="C2" t="n">
-        <v>3.903428872085318</v>
+        <v>6.007314202286233</v>
       </c>
       <c r="D2" t="n">
-        <v>25.28785736598934</v>
+        <v>13.2192328376833</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.54874021341174</v>
+        <v>3.789546138392688</v>
       </c>
       <c r="C3" t="n">
-        <v>39.08828484458675</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4311297486765</v>
+        <v>53.20581683165589</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.61249706092554</v>
+        <v>14.58778913740336</v>
       </c>
       <c r="C4" t="n">
-        <v>156.8921188679785</v>
+        <v>63.44348189154163</v>
       </c>
       <c r="D4" t="n">
-        <v>170.6248057549829</v>
+        <v>124.1940298303343</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>33.23215978875454</v>
       </c>
       <c r="C5" t="n">
-        <v>236.4784782604505</v>
+        <v>146.6731070144735</v>
       </c>
       <c r="D5" t="n">
-        <v>118.3251420543468</v>
+        <v>129.8115901940345</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>38.80259626265094</v>
       </c>
       <c r="C6" t="n">
-        <v>206.3702396666093</v>
+        <v>232.2923060495421</v>
       </c>
       <c r="D6" t="n">
-        <v>56.99634471775284</v>
+        <v>81.30834486572085</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>149.5368650677614</v>
+        <v>250.8650091184832</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>104.1437964665016</v>
+        <v>160.7219166622453</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
         <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.284526907782328</v>
+        <v>0.553705705195201</v>
       </c>
       <c r="C2" t="n">
-        <v>1.948769192929919</v>
+        <v>3.122939447209104</v>
       </c>
       <c r="D2" t="n">
-        <v>17.88253443285565</v>
+        <v>9.518043992672826</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>5.28180264884784</v>
       </c>
       <c r="C3" t="n">
-        <v>31.98043146583985</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D3" t="n">
-        <v>112.3168461043563</v>
+        <v>58.65451659022568</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.79041437957247</v>
+        <v>23.13881164139307</v>
       </c>
       <c r="C4" t="n">
-        <v>152.2337260113274</v>
+        <v>85.9824456856399</v>
       </c>
       <c r="D4" t="n">
-        <v>184.3447299218321</v>
+        <v>128.1632357986041</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.79728661350221</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>287.3575530330414</v>
+        <v>206.9033286700153</v>
       </c>
       <c r="D5" t="n">
-        <v>121.6876279413922</v>
+        <v>119.2578023733813</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.42396044398116</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>227.9451272151372</v>
+        <v>224.4029814982147</v>
       </c>
       <c r="D6" t="n">
-        <v>55.18502020341747</v>
+        <v>68.14605339488386</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>147.979813208826</v>
+        <v>113.0060329927376</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>73.8519710519663</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
         <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.033600406122644</v>
+        <v>0.4005530633326986</v>
       </c>
       <c r="C2" t="n">
-        <v>11.52473630015331</v>
+        <v>1.75438314748905</v>
       </c>
       <c r="D2" t="n">
-        <v>15.3437348696734</v>
+        <v>7.15301377314226</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.84125997154828</v>
+        <v>3.568652904937156</v>
       </c>
       <c r="C3" t="n">
-        <v>20.238728923048</v>
+        <v>15.61469723604552</v>
       </c>
       <c r="D3" t="n">
-        <v>103.0933264229576</v>
+        <v>52.85238765812704</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.27615850899639</v>
+        <v>15.67262035059608</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0206203395811</v>
+        <v>64.03056701868123</v>
       </c>
       <c r="D4" t="n">
-        <v>194.2358380421187</v>
+        <v>123.198537658228</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.20948178056562</v>
+        <v>23.29196428325558</v>
       </c>
       <c r="C5" t="n">
-        <v>283.6023680642974</v>
+        <v>165.9644494029233</v>
       </c>
       <c r="D5" t="n">
-        <v>149.2747384307276</v>
+        <v>122.8411814938822</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>13.6050596854523</v>
       </c>
       <c r="C6" t="n">
-        <v>326.1994192038622</v>
+        <v>226.8180808506619</v>
       </c>
       <c r="D6" t="n">
-        <v>72.49323222928874</v>
+        <v>74.02279515250527</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>218.6460129605114</v>
+        <v>149.2374320179661</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>119.3314334511998</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>50.47655821384974</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.942878706704438</v>
+        <v>0.2905973204570559</v>
       </c>
       <c r="C2" t="n">
-        <v>6.271404334728625</v>
+        <v>4.477751279069702</v>
       </c>
       <c r="D2" t="n">
-        <v>11.45405046544754</v>
+        <v>10.99655603526852</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.86932974434394</v>
+        <v>2.366011967234813</v>
       </c>
       <c r="C3" t="n">
-        <v>30.94468763785946</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="D3" t="n">
-        <v>95.68113125589414</v>
+        <v>46.30903920932204</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.02166486941822</v>
+        <v>11.12909197534184</v>
       </c>
       <c r="C4" t="n">
-        <v>95.23541779816608</v>
+        <v>50.02986300841746</v>
       </c>
       <c r="D4" t="n">
-        <v>198.6900273762865</v>
+        <v>122.1775200458113</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.57196766761096</v>
+        <v>23.80738182798515</v>
       </c>
       <c r="C5" t="n">
-        <v>271.3550654538184</v>
+        <v>139.4818050808656</v>
       </c>
       <c r="D5" t="n">
-        <v>167.6825078853552</v>
+        <v>139.8990478551705</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.30449032369931</v>
+        <v>22.70193391300324</v>
       </c>
       <c r="C6" t="n">
-        <v>377.5605320992384</v>
+        <v>250.0030346341545</v>
       </c>
       <c r="D6" t="n">
-        <v>86.98382834397167</v>
+        <v>94.99390786292139</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.83380690054181</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>286.257995604285</v>
+        <v>244.6966882927005</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>47.4301950875719</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>157.5508715775281</v>
+        <v>131.4314739060417</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>53.80468293124643</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>23.85156047467625</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.438661297349077</v>
+        <v>0.6361725123519331</v>
       </c>
       <c r="C2" t="n">
-        <v>12.02640937702343</v>
+        <v>9.918597056005526</v>
       </c>
       <c r="D2" t="n">
-        <v>14.41794678456866</v>
+        <v>12.05978879896782</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.439504176333081</v>
+        <v>1.629701189049706</v>
       </c>
       <c r="C3" t="n">
-        <v>28.10743677258618</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="D3" t="n">
-        <v>85.40714153095126</v>
+        <v>44.3700874934346</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.50366193447439</v>
+        <v>7.759733854366789</v>
       </c>
       <c r="C4" t="n">
-        <v>87.57778570504097</v>
+        <v>36.90978668886309</v>
       </c>
       <c r="D4" t="n">
-        <v>199.3792142646677</v>
+        <v>116.9830929426414</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.03200643027521</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="C5" t="n">
-        <v>230.9070600388499</v>
+        <v>114.9626561673015</v>
       </c>
       <c r="D5" t="n">
-        <v>189.3300447639974</v>
+        <v>152.0481756952248</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="C6" t="n">
-        <v>402.2750488059476</v>
+        <v>237.1627564103105</v>
       </c>
       <c r="D6" t="n">
-        <v>107.5121728397725</v>
+        <v>115.6027556704704</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>17.90609637775757</v>
       </c>
       <c r="C7" t="n">
-        <v>377.8845088416398</v>
+        <v>304.4036384218788</v>
       </c>
       <c r="D7" t="n">
-        <v>53.29908286355933</v>
+        <v>61.20411537815465</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>233.1552622815749</v>
+        <v>225.8117894538088</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>99.17811657842124</v>
+        <v>105.8343660132146</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>44.27191272300992</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.845906668162256</v>
+        <v>4.282383485924587</v>
       </c>
       <c r="C2" t="n">
-        <v>5.325981295538947</v>
+        <v>6.698464586075987</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45841942462103</v>
+        <v>16.48943444052943</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.820160243673586</v>
+        <v>1.16337102953247</v>
       </c>
       <c r="C2" t="n">
-        <v>7.312056901230244</v>
+        <v>12.73326772408113</v>
       </c>
       <c r="D2" t="n">
-        <v>10.84143989799753</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.41910845872215</v>
+        <v>1.860411899547706</v>
       </c>
       <c r="C3" t="n">
-        <v>37.87582642984194</v>
+        <v>26.3942870286755</v>
       </c>
       <c r="D3" t="n">
-        <v>91.33689766460201</v>
+        <v>43.55032816038851</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.89702396870788</v>
+        <v>5.500732386894879</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2570826675843</v>
+        <v>36.15678619970578</v>
       </c>
       <c r="D4" t="n">
-        <v>200.6554862801886</v>
+        <v>113.1542768960789</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.10252803406495</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="C5" t="n">
-        <v>343.7835023346269</v>
+        <v>91.62160449883359</v>
       </c>
       <c r="D5" t="n">
-        <v>167.2407214184442</v>
+        <v>158.6258853136784</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.17487426454295</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C6" t="n">
-        <v>311.950333024424</v>
+        <v>213.3740277887061</v>
       </c>
       <c r="D6" t="n">
-        <v>82.51589454194442</v>
+        <v>132.1864378906076</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>163.9695380678938</v>
+        <v>325.1244054677119</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>76.83452057746811</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>73.1009340582175</v>
+        <v>305.0879165717388</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>183.823421890877</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.21418523044183</v>
+        <v>79.14849991637786</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>15.81497376771187</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.585383673638358</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.059747741238813</v>
+        <v>6.709263810822701</v>
       </c>
       <c r="C2" t="n">
-        <v>6.369579105153306</v>
+        <v>7.69788374899924</v>
       </c>
       <c r="D2" t="n">
-        <v>19.51910785583508</v>
+        <v>14.99717793007427</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.29853341754904</v>
+        <v>7.078400947619503</v>
       </c>
       <c r="C3" t="n">
-        <v>13.4204911170539</v>
+        <v>13.22414157620454</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79908587799467</v>
+        <v>14.23534171157875</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39725927996997</v>
+        <v>11.67759699758637</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13859270101928</v>
+        <v>59.94499792094339</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576148150584703</v>
+        <v>0.7785064665057583</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.458116324984766</v>
+        <v>3.494040079414398</v>
       </c>
       <c r="C2" t="n">
-        <v>3.757148464152543</v>
+        <v>4.568072067860409</v>
       </c>
       <c r="D2" t="n">
-        <v>27.52722387937632</v>
+        <v>18.71800172916969</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6973850273805</v>
+        <v>17.26403337918016</v>
       </c>
       <c r="C3" t="n">
-        <v>20.56270566544944</v>
+        <v>24.45533531278805</v>
       </c>
       <c r="D3" t="n">
-        <v>29.89421759431538</v>
+        <v>23.85646921319749</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.06077054667207</v>
+        <v>8.831802347404306</v>
       </c>
       <c r="C4" t="n">
-        <v>21.02020009562846</v>
+        <v>22.05398042820035</v>
       </c>
       <c r="D4" t="n">
-        <v>24.40232093675872</v>
+        <v>21.81148874525138</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43924748411346</v>
+        <v>13.62877826093069</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13474912189615</v>
+        <v>73.75574117680135</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250367891392307</v>
+        <v>1.603385677756551</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.643666641087413</v>
+        <v>3.000220984178252</v>
       </c>
       <c r="C2" t="n">
-        <v>4.636794407157685</v>
+        <v>3.108213231645402</v>
       </c>
       <c r="D2" t="n">
-        <v>21.00154688924777</v>
+        <v>29.80095156241193</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.86151682043897</v>
+        <v>14.32369900496096</v>
       </c>
       <c r="C3" t="n">
-        <v>16.95969159086365</v>
+        <v>20.24854640009046</v>
       </c>
       <c r="D3" t="n">
-        <v>44.97877107006762</v>
+        <v>33.81139093426015</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.72964383290041</v>
+        <v>23.63655772744621</v>
       </c>
       <c r="C4" t="n">
-        <v>38.95182191369645</v>
+        <v>46.30314872309656</v>
       </c>
       <c r="D4" t="n">
-        <v>33.89778473223387</v>
+        <v>29.25215459573796</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.79922474671492</v>
+        <v>8.369399178704059</v>
       </c>
       <c r="C5" t="n">
-        <v>24.44551783574558</v>
+        <v>26.45810062945155</v>
       </c>
       <c r="D5" t="n">
-        <v>31.41592653589794</v>
+        <v>27.63619787454772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7313147224126</v>
+        <v>14.84008874392123</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0610198067169</v>
+        <v>87.39163371420281</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18282868060315</v>
+        <v>2.473348123986872</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.481678269886689</v>
+        <v>1.700387023755476</v>
       </c>
       <c r="C2" t="n">
-        <v>10.78351678344696</v>
+        <v>7.348381566287376</v>
       </c>
       <c r="D2" t="n">
-        <v>25.27705814124263</v>
+        <v>27.99355403889355</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.34119053718816</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C3" t="n">
-        <v>17.54874021341174</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="D3" t="n">
-        <v>50.93307089632452</v>
+        <v>49.80406103644069</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.6095107600838</v>
+        <v>26.32949168019521</v>
       </c>
       <c r="C4" t="n">
-        <v>40.90451809744336</v>
+        <v>48.98331995569036</v>
       </c>
       <c r="D4" t="n">
-        <v>48.01335322389451</v>
+        <v>39.61548336176729</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.54369260617026</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="C5" t="n">
-        <v>49.84823968313181</v>
+        <v>60.74563920027141</v>
       </c>
       <c r="D5" t="n">
-        <v>35.9810533606456</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>26.28433128579986</v>
+        <v>28.05540414426111</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05768348922439</v>
+        <v>16.08344088432908</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8048875249401</v>
+        <v>101.5796266378679</v>
       </c>
       <c r="D21" t="n">
-        <v>6.019227829741463</v>
+        <v>3.385987554595597</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.627377840742716</v>
+        <v>3.00709321810798</v>
       </c>
       <c r="C2" t="n">
-        <v>15.95241844630642</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="D2" t="n">
-        <v>32.87774886752143</v>
+        <v>22.16491791878024</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.04390090925062</v>
+        <v>8.659014751456867</v>
       </c>
       <c r="C3" t="n">
-        <v>29.59969328304133</v>
+        <v>23.18397203578843</v>
       </c>
       <c r="D3" t="n">
-        <v>55.33620934987147</v>
+        <v>59.99951094504382</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.23265851037327</v>
+        <v>24.92559246312227</v>
       </c>
       <c r="C4" t="n">
-        <v>35.32720938961722</v>
+        <v>42.44880723622359</v>
       </c>
       <c r="D4" t="n">
-        <v>54.03735713715294</v>
+        <v>54.42023874180919</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.30392518215579</v>
+        <v>31.17048960983623</v>
       </c>
       <c r="C5" t="n">
-        <v>47.5411325781518</v>
+        <v>77.14082586119314</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85833489761475</v>
+        <v>38.8772090881737</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="C6" t="n">
-        <v>36.50825187782615</v>
+        <v>64.12088780747193</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>29.64387192973244</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058214634336861</v>
+        <v>17.35378957865473</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17076219690807</v>
+        <v>115.402700698054</v>
       </c>
       <c r="D21" t="n">
-        <v>4.411384146460538</v>
+        <v>4.338447394663683</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.705516746454962</v>
+        <v>3.873976440957914</v>
       </c>
       <c r="C2" t="n">
-        <v>11.15461741565226</v>
+        <v>9.781152377410972</v>
       </c>
       <c r="D2" t="n">
-        <v>39.85012106308228</v>
+        <v>27.71375594318321</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.55364895193297</v>
+        <v>9.542587685278997</v>
       </c>
       <c r="C3" t="n">
-        <v>50.71217766286899</v>
+        <v>23.21833320543707</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5813685384927</v>
+        <v>63.19019098384595</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.76793199336603</v>
+        <v>20.53521672973053</v>
       </c>
       <c r="C4" t="n">
-        <v>59.76781848684157</v>
+        <v>50.22130381074558</v>
       </c>
       <c r="D4" t="n">
-        <v>69.9779946110084</v>
+        <v>69.78655380868027</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>34.53297549688156</v>
       </c>
       <c r="C5" t="n">
-        <v>58.48761948050374</v>
+        <v>77.7544181763474</v>
       </c>
       <c r="D5" t="n">
-        <v>48.47379289718628</v>
+        <v>49.03829782712819</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.49438423677967</v>
+        <v>30.14849024971531</v>
       </c>
       <c r="C6" t="n">
-        <v>59.16993413495527</v>
+        <v>93.38384162795661</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>40.6139207769863</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>39.04606969330414</v>
+        <v>60.54536266860504</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280241165549317</v>
+        <v>18.64635119948622</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53250209257416</v>
+        <v>128.7486154250239</v>
       </c>
       <c r="D21" t="n">
-        <v>5.460180874161987</v>
+        <v>5.32752891413892</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.730060439061132</v>
+        <v>3.390956570468483</v>
       </c>
       <c r="C2" t="n">
-        <v>9.232355410737005</v>
+        <v>6.024985660962675</v>
       </c>
       <c r="D2" t="n">
-        <v>32.80509953740717</v>
+        <v>21.74767514447534</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84679060487527</v>
+        <v>13.39594742444773</v>
       </c>
       <c r="C3" t="n">
-        <v>46.32376542488575</v>
+        <v>37.59111959561037</v>
       </c>
       <c r="D3" t="n">
-        <v>85.31387549904782</v>
+        <v>70.24404823885929</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.68157925312132</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C4" t="n">
-        <v>98.0815043927776</v>
+        <v>70.62889333892403</v>
       </c>
       <c r="D4" t="n">
-        <v>89.14760028413161</v>
+        <v>64.4517367838031</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.09118902997049</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>88.13640014875742</v>
+        <v>55.78781329382501</v>
       </c>
       <c r="D5" t="n">
-        <v>62.21826075664162</v>
+        <v>38.85266539556753</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.03402667894593</v>
+        <v>9.499390786292139</v>
       </c>
       <c r="C6" t="n">
-        <v>77.88695411642071</v>
+        <v>39.84913931537804</v>
       </c>
       <c r="D6" t="n">
-        <v>43.9548082145382</v>
+        <v>25.55980148006571</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>64.43799231594365</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>38.38633523605029</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487625199765883</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.17173664733691</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551672049795148</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
